--- a/backend/data/financials_by_company/1EVD.MI.xlsx
+++ b/backend/data/financials_by_company/1EVD.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,202 +659,124 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization In Income Statement</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Depreciation Income Statement</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1499993.565552</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.330468</v>
-      </c>
-      <c r="D2" t="n">
-        <v>624843000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4539000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4539000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>318867000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>93471000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2068013000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>629382000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>535911000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>38145000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>12323000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>49341000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>315827993.565552</v>
-      </c>
-      <c r="P2" t="n">
-        <v>318867000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2381457000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>95991300</v>
-      </c>
-      <c r="S2" t="n">
-        <v>95991300</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>318867000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>318867000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>318867000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-31691000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>350559000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>350559000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>173029000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>523588000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5177000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-23084000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>17907000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>38145000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1127000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12323000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>49341000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>427122000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>313444000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>36267000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>309873000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>156483000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>153390000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>740566000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2068013000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2808579000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2808579000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>3380000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12014504.233642</v>
+        <v>13921455.48173</v>
       </c>
       <c r="C3" t="n">
-        <v>0.331407</v>
+        <v>0.256371</v>
       </c>
       <c r="D3" t="n">
-        <v>544401000</v>
+        <v>352665000</v>
       </c>
       <c r="E3" t="n">
-        <v>-36253000</v>
+        <v>54302000</v>
       </c>
       <c r="F3" t="n">
-        <v>-36253000</v>
+        <v>54302000</v>
       </c>
       <c r="G3" t="n">
-        <v>274641000</v>
+        <v>203748000</v>
       </c>
       <c r="H3" t="n">
-        <v>91635000</v>
+        <v>60689000</v>
       </c>
       <c r="I3" t="n">
-        <v>1755395000</v>
+        <v>1477532000</v>
       </c>
       <c r="J3" t="n">
-        <v>508148000</v>
+        <v>406967000</v>
       </c>
       <c r="K3" t="n">
-        <v>416513000</v>
+        <v>346278000</v>
       </c>
       <c r="L3" t="n">
-        <v>25576000</v>
+        <v>-189000</v>
       </c>
       <c r="M3" t="n">
-        <v>7409000</v>
+        <v>5081000</v>
       </c>
       <c r="N3" t="n">
-        <v>32554000</v>
+        <v>5357000</v>
       </c>
       <c r="O3" t="n">
-        <v>298879495.766358</v>
+        <v>163367455.48173</v>
       </c>
       <c r="P3" t="n">
-        <v>274641000</v>
+        <v>203748000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1966389000</v>
+        <v>1661711000</v>
       </c>
       <c r="R3" t="n">
         <v>95991300</v>
@@ -863,142 +785,144 @@
         <v>95991300</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>274641000</v>
+        <v>203748000</v>
       </c>
       <c r="W3" t="n">
-        <v>274641000</v>
+        <v>203748000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>274641000</v>
+        <v>203748000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1118000</v>
+        <v>-49977000</v>
       </c>
       <c r="AA3" t="n">
-        <v>273524000</v>
+        <v>253725000</v>
       </c>
       <c r="AB3" t="n">
-        <v>273524000</v>
+        <v>253724000</v>
       </c>
       <c r="AC3" t="n">
-        <v>135580000</v>
+        <v>87473000</v>
       </c>
       <c r="AD3" t="n">
-        <v>409104000</v>
+        <v>341197000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6115000</v>
+        <v>48326000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-15498000</v>
+        <v>-57820000</v>
       </c>
       <c r="AG3" t="n">
-        <v>21613000</v>
+        <v>9494000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>25576000</v>
+        <v>-189000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-431000</v>
+        <v>465000</v>
       </c>
       <c r="AK3" t="n">
-        <v>7409000</v>
+        <v>5081000</v>
       </c>
       <c r="AL3" t="n">
-        <v>32554000</v>
+        <v>5357000</v>
       </c>
       <c r="AM3" t="n">
-        <v>392163000</v>
+        <v>264092000</v>
       </c>
       <c r="AN3" t="n">
-        <v>210994000</v>
+        <v>184179000</v>
       </c>
       <c r="AO3" t="n">
-        <v>25962000</v>
+        <v>9596000</v>
       </c>
       <c r="AP3" t="n">
-        <v>244086000</v>
+        <v>197719000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>125063000</v>
+        <v>101182000</v>
       </c>
       <c r="AR3" t="n">
-        <v>119023000</v>
+        <v>96537000</v>
       </c>
       <c r="AS3" t="n">
-        <v>603157000</v>
+        <v>448271000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1755395000</v>
+        <v>1477532000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2358552000</v>
+        <v>1925803000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2358552000</v>
-      </c>
+        <v>1925803000</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>13921455.48173</v>
+        <v>-12014504.233642</v>
       </c>
       <c r="C4" t="n">
-        <v>0.256371</v>
+        <v>0.331407</v>
       </c>
       <c r="D4" t="n">
-        <v>352665000</v>
+        <v>544401000</v>
       </c>
       <c r="E4" t="n">
-        <v>54302000</v>
+        <v>-36253000</v>
       </c>
       <c r="F4" t="n">
-        <v>54302000</v>
+        <v>-36253000</v>
       </c>
       <c r="G4" t="n">
-        <v>203748000</v>
+        <v>274641000</v>
       </c>
       <c r="H4" t="n">
-        <v>60689000</v>
+        <v>91635000</v>
       </c>
       <c r="I4" t="n">
-        <v>1477532000</v>
+        <v>1755395000</v>
       </c>
       <c r="J4" t="n">
-        <v>406967000</v>
+        <v>508148000</v>
       </c>
       <c r="K4" t="n">
-        <v>346278000</v>
+        <v>416513000</v>
       </c>
       <c r="L4" t="n">
-        <v>-189000</v>
+        <v>25576000</v>
       </c>
       <c r="M4" t="n">
-        <v>5081000</v>
+        <v>7409000</v>
       </c>
       <c r="N4" t="n">
-        <v>5357000</v>
+        <v>32554000</v>
       </c>
       <c r="O4" t="n">
-        <v>163367455.48173</v>
+        <v>298879495.766358</v>
       </c>
       <c r="P4" t="n">
-        <v>203748000</v>
+        <v>274641000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1661711000</v>
+        <v>1966389000</v>
       </c>
       <c r="R4" t="n">
         <v>95991300</v>
@@ -1007,142 +931,144 @@
         <v>95991300</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="V4" t="n">
-        <v>203748000</v>
+        <v>274641000</v>
       </c>
       <c r="W4" t="n">
-        <v>203748000</v>
+        <v>274641000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>203748000</v>
+        <v>274641000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-49977000</v>
+        <v>1118000</v>
       </c>
       <c r="AA4" t="n">
-        <v>253725000</v>
+        <v>273524000</v>
       </c>
       <c r="AB4" t="n">
-        <v>253724000</v>
+        <v>273524000</v>
       </c>
       <c r="AC4" t="n">
-        <v>87473000</v>
+        <v>135580000</v>
       </c>
       <c r="AD4" t="n">
-        <v>341197000</v>
+        <v>409104000</v>
       </c>
       <c r="AE4" t="n">
-        <v>48326000</v>
+        <v>-6115000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-57820000</v>
+        <v>-15498000</v>
       </c>
       <c r="AG4" t="n">
-        <v>9494000</v>
+        <v>21613000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-189000</v>
+        <v>25576000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>465000</v>
+        <v>-431000</v>
       </c>
       <c r="AK4" t="n">
-        <v>5081000</v>
+        <v>7409000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5357000</v>
+        <v>32554000</v>
       </c>
       <c r="AM4" t="n">
-        <v>264092000</v>
+        <v>392163000</v>
       </c>
       <c r="AN4" t="n">
-        <v>184179000</v>
+        <v>210994000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9596000</v>
+        <v>25962000</v>
       </c>
       <c r="AP4" t="n">
-        <v>197719000</v>
+        <v>244086000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>101182000</v>
+        <v>125063000</v>
       </c>
       <c r="AR4" t="n">
-        <v>96537000</v>
+        <v>119023000</v>
       </c>
       <c r="AS4" t="n">
-        <v>448271000</v>
+        <v>603157000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1477532000</v>
+        <v>1755395000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1925803000</v>
+        <v>2358552000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1925803000</v>
-      </c>
+        <v>2358552000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>66521987.647409</v>
+        <v>1618961.991108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.339005</v>
+        <v>0.330468</v>
       </c>
       <c r="D5" t="n">
-        <v>4951000</v>
+        <v>624483000</v>
       </c>
       <c r="E5" t="n">
-        <v>196227000</v>
+        <v>4899000</v>
       </c>
       <c r="F5" t="n">
-        <v>196227000</v>
+        <v>4899000</v>
       </c>
       <c r="G5" t="n">
-        <v>87909000</v>
+        <v>318867000</v>
       </c>
       <c r="H5" t="n">
-        <v>55501000</v>
+        <v>93471000</v>
       </c>
       <c r="I5" t="n">
-        <v>327110000</v>
+        <v>2068013000</v>
       </c>
       <c r="J5" t="n">
-        <v>201178000</v>
+        <v>629382000</v>
       </c>
       <c r="K5" t="n">
-        <v>145677000</v>
+        <v>535911000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1689000</v>
+        <v>38145000</v>
       </c>
       <c r="M5" t="n">
-        <v>4573000</v>
+        <v>12323000</v>
       </c>
       <c r="N5" t="n">
-        <v>859000</v>
+        <v>49341000</v>
       </c>
       <c r="O5" t="n">
-        <v>-41796012.352591</v>
+        <v>315586961.991108</v>
       </c>
       <c r="P5" t="n">
-        <v>87909000</v>
+        <v>318867000</v>
       </c>
       <c r="Q5" t="n">
-        <v>461913000</v>
+        <v>2381817000</v>
       </c>
       <c r="R5" t="n">
         <v>95991300</v>
@@ -1151,89 +1077,245 @@
         <v>95991300</v>
       </c>
       <c r="T5" t="n">
-        <v>0.92</v>
+        <v>3.32</v>
       </c>
       <c r="U5" t="n">
-        <v>0.92</v>
+        <v>3.32</v>
       </c>
       <c r="V5" t="n">
-        <v>87909000</v>
+        <v>318867000</v>
       </c>
       <c r="W5" t="n">
-        <v>87909000</v>
+        <v>318867000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>87909000</v>
+        <v>318867000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5360000</v>
+        <v>-31691000</v>
       </c>
       <c r="AA5" t="n">
-        <v>93269000</v>
+        <v>350559000</v>
       </c>
       <c r="AB5" t="n">
-        <v>93269000</v>
+        <v>350559000</v>
       </c>
       <c r="AC5" t="n">
-        <v>47835000</v>
+        <v>173029000</v>
       </c>
       <c r="AD5" t="n">
-        <v>141104000</v>
+        <v>523588000</v>
       </c>
       <c r="AE5" t="n">
-        <v>196227000</v>
+        <v>5537000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-196227000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>3380000</v>
-      </c>
+        <v>-23444000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17907000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-1689000</v>
+        <v>38145000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2025000</v>
+        <v>-1127000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4573000</v>
+        <v>12323000</v>
       </c>
       <c r="AL5" t="n">
-        <v>859000</v>
+        <v>49341000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-54092000</v>
+        <v>426762000</v>
       </c>
       <c r="AN5" t="n">
-        <v>134803000</v>
+        <v>313804000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3887000</v>
+        <v>27726000</v>
       </c>
       <c r="AP5" t="n">
-        <v>143950000</v>
+        <v>314798000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>81758000</v>
+        <v>156483000</v>
       </c>
       <c r="AR5" t="n">
-        <v>62192000</v>
+        <v>158315000</v>
       </c>
       <c r="AS5" t="n">
-        <v>80711000</v>
+        <v>740566000</v>
       </c>
       <c r="AT5" t="n">
-        <v>327110000</v>
+        <v>2068013000</v>
       </c>
       <c r="AU5" t="n">
-        <v>407821000</v>
+        <v>2808579000</v>
       </c>
       <c r="AV5" t="n">
-        <v>407821000</v>
+        <v>2808579000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3616000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3616000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-5020393.165241</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.336962</v>
+      </c>
+      <c r="D6" t="n">
+        <v>587447000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-14899000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-14899000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>277265000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>101601000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2249163000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>572548000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>470947000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19905000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11794000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32222000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>287143606.834759</v>
+      </c>
+      <c r="P6" t="n">
+        <v>277265000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2608950000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>95991300</v>
+      </c>
+      <c r="S6" t="n">
+        <v>95991300</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V6" t="n">
+        <v>277265000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>277265000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>277265000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-27172000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>304436000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>304436000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>154717000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>459153000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6115000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-12664000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6549000</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>19905000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>523000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>11794000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32222000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>470345000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>359787000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>19065000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>357485000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>190521000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>166964000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>830132000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2249163000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3079295000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3079295000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3619000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3619000</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH5"/>
+  <dimension ref="A1:CI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,258 +1758,116 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>8700</v>
-      </c>
-      <c r="C2" t="n">
-        <v>95991300</v>
-      </c>
-      <c r="D2" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>120054000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18031000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1029567000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-91304000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18031000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>117444000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1026957000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1026957000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1182535000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>155578000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1026957000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>52000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>924527000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2884745000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>387350000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>37801000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>16053000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>1452000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>37909000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>67531000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>95479000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>95479000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>4153000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2497395000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>822665000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24575000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>21965000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2610000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>50384000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>21167000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>497704000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4399000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>138252000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>355053000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4067280000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1661188000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23079000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16092000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>32880000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>123149000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>123149000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>32062000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>32062000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>14515000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14515000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>19827000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>4462000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>1701000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>1008926000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>266906000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>742020000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>422282000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-239631000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>661913000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>204400000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>235659000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>16624000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>205230000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2406091000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>12083000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>12728000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>216603000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>15555000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>10145000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4364000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1046000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>50530000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>115874000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>187179000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>-8530000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>195709000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1795539000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>276937000</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1518602000</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>383018000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1135584000</v>
-      </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>8700</v>
@@ -1939,43 +1879,43 @@
         <v>96000000</v>
       </c>
       <c r="E3" t="n">
-        <v>123259000</v>
+        <v>121292000</v>
       </c>
       <c r="F3" t="n">
-        <v>351991000</v>
+        <v>223485000</v>
       </c>
       <c r="G3" t="n">
-        <v>898641000</v>
+        <v>731924000</v>
       </c>
       <c r="H3" t="n">
-        <v>203932000</v>
+        <v>142752000</v>
       </c>
       <c r="I3" t="n">
-        <v>351991000</v>
+        <v>223485000</v>
       </c>
       <c r="J3" t="n">
-        <v>121432000</v>
+        <v>120938000</v>
       </c>
       <c r="K3" t="n">
-        <v>896814000</v>
+        <v>731570000</v>
       </c>
       <c r="L3" t="n">
-        <v>896814000</v>
+        <v>731771000</v>
       </c>
       <c r="M3" t="n">
-        <v>1014564000</v>
+        <v>837372000</v>
       </c>
       <c r="N3" t="n">
-        <v>117750000</v>
+        <v>105802000</v>
       </c>
       <c r="O3" t="n">
-        <v>896814000</v>
+        <v>731570000</v>
       </c>
       <c r="P3" t="n">
         <v>52000</v>
       </c>
       <c r="Q3" t="n">
-        <v>788421000</v>
+        <v>629447000</v>
       </c>
       <c r="R3" t="n">
         <v>1890000</v>
@@ -1987,199 +1927,204 @@
         <v>96000000</v>
       </c>
       <c r="U3" t="n">
-        <v>2180775000</v>
+        <v>1771804000</v>
       </c>
       <c r="V3" t="n">
-        <v>235008000</v>
+        <v>178313000</v>
       </c>
       <c r="W3" t="n">
-        <v>4147000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>12052000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14672000</v>
+      </c>
       <c r="Y3" t="n">
-        <v>56381000</v>
+        <v>14672000</v>
       </c>
       <c r="Z3" t="n">
-        <v>9978000</v>
+        <v>6000000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>9387000</v>
+        <v>1303000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15268000</v>
+        <v>7381000</v>
       </c>
       <c r="AD3" t="n">
-        <v>33707000</v>
+        <v>27022000</v>
       </c>
       <c r="AE3" t="n">
-        <v>100327000</v>
+        <v>103090000</v>
       </c>
       <c r="AF3" t="n">
-        <v>100327000</v>
+        <v>102889000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1400000</v>
+        <v>201000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3973000</v>
+        <v>4957000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1945767000</v>
+        <v>1593491000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>726350000</v>
+        <v>572302000</v>
       </c>
       <c r="AK3" t="n">
-        <v>22932000</v>
+        <v>18202000</v>
       </c>
       <c r="AL3" t="n">
-        <v>21105000</v>
+        <v>18049000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1827000</v>
+        <v>153000</v>
       </c>
       <c r="AN3" t="n">
-        <v>42485000</v>
+        <v>38615000</v>
       </c>
       <c r="AO3" t="n">
-        <v>28955000</v>
+        <v>39762000</v>
       </c>
       <c r="AP3" t="n">
-        <v>413426000</v>
+        <v>361552000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9138000</v>
+        <v>8154000</v>
       </c>
       <c r="AR3" t="n">
-        <v>121029000</v>
+        <v>120776000</v>
       </c>
       <c r="AS3" t="n">
-        <v>283259000</v>
+        <v>232622000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3195339000</v>
+        <v>2609176000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1045640000</v>
+        <v>872933000</v>
       </c>
       <c r="AV3" t="n">
-        <v>12157000</v>
+        <v>14189000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1937000</v>
+        <v>2299000</v>
       </c>
       <c r="AX3" t="n">
-        <v>32952000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1611000</v>
-      </c>
+        <v>25356000</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>28490000</v>
+        <v>1106000</v>
       </c>
       <c r="BA3" t="n">
-        <v>28490000</v>
+        <v>1106000</v>
       </c>
       <c r="BB3" t="n">
-        <v>108234000</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>134867000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1300000</v>
+      </c>
       <c r="BD3" t="n">
-        <v>108234000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>133311000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>256000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>544823000</v>
+        <v>508085000</v>
       </c>
       <c r="BG3" t="n">
-        <v>157131000</v>
+        <v>146346000</v>
       </c>
       <c r="BH3" t="n">
-        <v>387692000</v>
+        <v>361739000</v>
       </c>
       <c r="BI3" t="n">
-        <v>315354000</v>
+        <v>179593000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-201862000</v>
+        <v>-66697000</v>
       </c>
       <c r="BK3" t="n">
-        <v>517216000</v>
+        <v>246290000</v>
       </c>
       <c r="BL3" t="n">
-        <v>109569000</v>
+        <v>22671000</v>
       </c>
       <c r="BM3" t="n">
-        <v>199965000</v>
+        <v>62636000</v>
       </c>
       <c r="BN3" t="n">
-        <v>11274000</v>
+        <v>3587000</v>
       </c>
       <c r="BO3" t="n">
-        <v>196408000</v>
+        <v>180067000</v>
       </c>
       <c r="BP3" t="n">
         <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2149699000</v>
+        <v>1736243000</v>
       </c>
       <c r="BR3" t="n">
-        <v>11485000</v>
+        <v>9982000</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>153440000</v>
+        <v>149440000</v>
       </c>
       <c r="BU3" t="n">
-        <v>14245000</v>
+        <v>5027000</v>
       </c>
       <c r="BV3" t="n">
-        <v>9630000</v>
+        <v>2120000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3611000</v>
+        <v>1978000</v>
       </c>
       <c r="BX3" t="n">
-        <v>1004000</v>
+        <v>930000</v>
       </c>
       <c r="BY3" t="n">
-        <v>35178000</v>
+        <v>45552000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>65415000</v>
+        <v>33556000</v>
       </c>
       <c r="CA3" t="n">
-        <v>166335000</v>
+        <v>158378000</v>
       </c>
       <c r="CB3" t="n">
-        <v>-5714000</v>
+        <v>-5580000</v>
       </c>
       <c r="CC3" t="n">
-        <v>172049000</v>
+        <v>158378000</v>
       </c>
       <c r="CD3" t="n">
-        <v>1703601000</v>
+        <v>1334308000</v>
       </c>
       <c r="CE3" t="n">
-        <v>675108000</v>
+        <v>185458000</v>
       </c>
       <c r="CF3" t="n">
-        <v>1028493000</v>
+        <v>1148850000</v>
       </c>
       <c r="CG3" t="n">
-        <v>98369000</v>
+        <v>91523000</v>
       </c>
       <c r="CH3" t="n">
-        <v>930124000</v>
-      </c>
+        <v>1057327000</v>
+      </c>
+      <c r="CI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>8700</v>
@@ -2191,43 +2136,43 @@
         <v>96000000</v>
       </c>
       <c r="E4" t="n">
-        <v>121292000</v>
+        <v>123259000</v>
       </c>
       <c r="F4" t="n">
-        <v>223485000</v>
+        <v>351991000</v>
       </c>
       <c r="G4" t="n">
-        <v>731924000</v>
+        <v>898641000</v>
       </c>
       <c r="H4" t="n">
-        <v>142752000</v>
+        <v>203932000</v>
       </c>
       <c r="I4" t="n">
-        <v>223485000</v>
+        <v>351991000</v>
       </c>
       <c r="J4" t="n">
-        <v>120938000</v>
+        <v>121432000</v>
       </c>
       <c r="K4" t="n">
-        <v>731570000</v>
+        <v>896814000</v>
       </c>
       <c r="L4" t="n">
-        <v>731771000</v>
+        <v>896814000</v>
       </c>
       <c r="M4" t="n">
-        <v>837372000</v>
+        <v>1014564000</v>
       </c>
       <c r="N4" t="n">
-        <v>105802000</v>
+        <v>117750000</v>
       </c>
       <c r="O4" t="n">
-        <v>731570000</v>
+        <v>896814000</v>
       </c>
       <c r="P4" t="n">
         <v>52000</v>
       </c>
       <c r="Q4" t="n">
-        <v>629447000</v>
+        <v>788421000</v>
       </c>
       <c r="R4" t="n">
         <v>1890000</v>
@@ -2239,203 +2184,200 @@
         <v>96000000</v>
       </c>
       <c r="U4" t="n">
-        <v>1771804000</v>
+        <v>2180775000</v>
       </c>
       <c r="V4" t="n">
-        <v>178313000</v>
+        <v>235008000</v>
       </c>
       <c r="W4" t="n">
-        <v>12052000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14672000</v>
-      </c>
+        <v>4147000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>14672000</v>
+        <v>56381000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6000000</v>
+        <v>9978000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>1303000</v>
+        <v>9387000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7381000</v>
+        <v>15268000</v>
       </c>
       <c r="AD4" t="n">
-        <v>27022000</v>
+        <v>33707000</v>
       </c>
       <c r="AE4" t="n">
-        <v>103090000</v>
+        <v>100327000</v>
       </c>
       <c r="AF4" t="n">
-        <v>102889000</v>
+        <v>100327000</v>
       </c>
       <c r="AG4" t="n">
-        <v>201000</v>
+        <v>1400000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4957000</v>
+        <v>3973000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1593491000</v>
+        <v>1945767000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>572302000</v>
+        <v>726350000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18202000</v>
+        <v>22932000</v>
       </c>
       <c r="AL4" t="n">
-        <v>18049000</v>
+        <v>21105000</v>
       </c>
       <c r="AM4" t="n">
-        <v>153000</v>
+        <v>1827000</v>
       </c>
       <c r="AN4" t="n">
-        <v>38615000</v>
+        <v>42485000</v>
       </c>
       <c r="AO4" t="n">
-        <v>39762000</v>
+        <v>28955000</v>
       </c>
       <c r="AP4" t="n">
-        <v>361552000</v>
+        <v>413426000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8154000</v>
+        <v>9138000</v>
       </c>
       <c r="AR4" t="n">
-        <v>120776000</v>
+        <v>121029000</v>
       </c>
       <c r="AS4" t="n">
-        <v>232622000</v>
+        <v>283259000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2609176000</v>
+        <v>3195339000</v>
       </c>
       <c r="AU4" t="n">
-        <v>872933000</v>
+        <v>1045640000</v>
       </c>
       <c r="AV4" t="n">
-        <v>14189000</v>
+        <v>12157000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2299000</v>
+        <v>1937000</v>
       </c>
       <c r="AX4" t="n">
-        <v>25356000</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+        <v>32952000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1611000</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>1106000</v>
+        <v>28490000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1106000</v>
+        <v>28490000</v>
       </c>
       <c r="BB4" t="n">
-        <v>134867000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1300000</v>
-      </c>
+        <v>108234000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>133311000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>256000</v>
-      </c>
+        <v>108234000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>508085000</v>
+        <v>544823000</v>
       </c>
       <c r="BG4" t="n">
-        <v>146346000</v>
+        <v>157131000</v>
       </c>
       <c r="BH4" t="n">
-        <v>361739000</v>
+        <v>387692000</v>
       </c>
       <c r="BI4" t="n">
-        <v>179593000</v>
+        <v>315354000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-66697000</v>
+        <v>-201862000</v>
       </c>
       <c r="BK4" t="n">
-        <v>246290000</v>
+        <v>517216000</v>
       </c>
       <c r="BL4" t="n">
-        <v>22671000</v>
+        <v>109569000</v>
       </c>
       <c r="BM4" t="n">
-        <v>62636000</v>
+        <v>199965000</v>
       </c>
       <c r="BN4" t="n">
-        <v>3587000</v>
+        <v>11274000</v>
       </c>
       <c r="BO4" t="n">
-        <v>180067000</v>
+        <v>196408000</v>
       </c>
       <c r="BP4" t="n">
         <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1736243000</v>
+        <v>2149699000</v>
       </c>
       <c r="BR4" t="n">
-        <v>9982000</v>
+        <v>11485000</v>
       </c>
       <c r="BS4" t="n">
         <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>149440000</v>
+        <v>153440000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5027000</v>
+        <v>14245000</v>
       </c>
       <c r="BV4" t="n">
-        <v>2120000</v>
+        <v>9630000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1978000</v>
+        <v>3611000</v>
       </c>
       <c r="BX4" t="n">
-        <v>930000</v>
+        <v>1004000</v>
       </c>
       <c r="BY4" t="n">
-        <v>45552000</v>
+        <v>35178000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>33556000</v>
+        <v>65415000</v>
       </c>
       <c r="CA4" t="n">
-        <v>158378000</v>
+        <v>166335000</v>
       </c>
       <c r="CB4" t="n">
-        <v>-5580000</v>
+        <v>-5714000</v>
       </c>
       <c r="CC4" t="n">
-        <v>158378000</v>
+        <v>172049000</v>
       </c>
       <c r="CD4" t="n">
-        <v>1334308000</v>
+        <v>1703601000</v>
       </c>
       <c r="CE4" t="n">
-        <v>185458000</v>
+        <v>675108000</v>
       </c>
       <c r="CF4" t="n">
-        <v>1148850000</v>
+        <v>1028493000</v>
       </c>
       <c r="CG4" t="n">
-        <v>91523000</v>
+        <v>98369000</v>
       </c>
       <c r="CH4" t="n">
-        <v>1057327000</v>
-      </c>
+        <v>930124000</v>
+      </c>
+      <c r="CI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>8700</v>
@@ -2447,43 +2389,43 @@
         <v>96000000</v>
       </c>
       <c r="E5" t="n">
-        <v>135583000</v>
+        <v>120054000</v>
       </c>
       <c r="F5" t="n">
-        <v>13479000</v>
+        <v>15146000</v>
       </c>
       <c r="G5" t="n">
-        <v>534542000</v>
+        <v>1029567000</v>
       </c>
       <c r="H5" t="n">
-        <v>-77725000</v>
+        <v>-94189000</v>
       </c>
       <c r="I5" t="n">
-        <v>13479000</v>
+        <v>15146000</v>
       </c>
       <c r="J5" t="n">
-        <v>130993000</v>
+        <v>117444000</v>
       </c>
       <c r="K5" t="n">
-        <v>529952000</v>
+        <v>1026957000</v>
       </c>
       <c r="L5" t="n">
-        <v>534414000</v>
+        <v>1026957000</v>
       </c>
       <c r="M5" t="n">
-        <v>585799000</v>
+        <v>1182535000</v>
       </c>
       <c r="N5" t="n">
-        <v>55847000</v>
+        <v>155578000</v>
       </c>
       <c r="O5" t="n">
-        <v>529952000</v>
+        <v>1026957000</v>
       </c>
       <c r="P5" t="n">
         <v>52000</v>
       </c>
       <c r="Q5" t="n">
-        <v>424609000</v>
+        <v>924527000</v>
       </c>
       <c r="R5" t="n">
         <v>1890000</v>
@@ -2495,193 +2437,445 @@
         <v>96000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1702037000</v>
+        <v>2884745000</v>
       </c>
       <c r="V5" t="n">
-        <v>225342000</v>
+        <v>387350000</v>
       </c>
       <c r="W5" t="n">
-        <v>34716000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14515000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14515000</v>
-      </c>
+        <v>37801000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>13201000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>19827000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>16053000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>1452000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>19827000</v>
+        <v>37909000</v>
       </c>
       <c r="AD5" t="n">
-        <v>20294000</v>
+        <v>67531000</v>
       </c>
       <c r="AE5" t="n">
-        <v>117482000</v>
+        <v>95479000</v>
       </c>
       <c r="AF5" t="n">
-        <v>113020000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4462000</v>
-      </c>
+        <v>95479000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>4557000</v>
+        <v>4153000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1476695000</v>
+        <v>2497395000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>673687000</v>
+        <v>822665000</v>
       </c>
       <c r="AK5" t="n">
-        <v>18101000</v>
+        <v>24575000</v>
       </c>
       <c r="AL5" t="n">
-        <v>17973000</v>
+        <v>21965000</v>
       </c>
       <c r="AM5" t="n">
-        <v>128000</v>
+        <v>2610000</v>
       </c>
       <c r="AN5" t="n">
-        <v>25766000</v>
+        <v>50384000</v>
       </c>
       <c r="AO5" t="n">
-        <v>37030000</v>
+        <v>21167000</v>
       </c>
       <c r="AP5" t="n">
-        <v>195441000</v>
+        <v>497704000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6420000</v>
+        <v>4399000</v>
       </c>
       <c r="AR5" t="n">
-        <v>69298000</v>
+        <v>138252000</v>
       </c>
       <c r="AS5" t="n">
-        <v>119723000</v>
+        <v>355053000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2287836000</v>
+        <v>4067280000</v>
       </c>
       <c r="AU5" t="n">
-        <v>888866000</v>
+        <v>1664073000</v>
       </c>
       <c r="AV5" t="n">
-        <v>10270000</v>
+        <v>23079000</v>
       </c>
       <c r="AW5" t="n">
-        <v>26916000</v>
+        <v>16092000</v>
       </c>
       <c r="AX5" t="n">
-        <v>30717000</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>32880000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1710000</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>2180000</v>
+        <v>123149000</v>
       </c>
       <c r="BA5" t="n">
-        <v>2180000</v>
+        <v>123149000</v>
       </c>
       <c r="BB5" t="n">
-        <v>115496000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1701000</v>
-      </c>
+        <v>32062000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>113795000</v>
+        <v>32062000</v>
       </c>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>516473000</v>
+        <v>1011811000</v>
       </c>
       <c r="BG5" t="n">
-        <v>153833000</v>
+        <v>266906000</v>
       </c>
       <c r="BH5" t="n">
-        <v>362640000</v>
+        <v>744905000</v>
       </c>
       <c r="BI5" t="n">
-        <v>169766000</v>
+        <v>422282000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-113444000</v>
+        <v>-239631000</v>
       </c>
       <c r="BK5" t="n">
-        <v>283210000</v>
+        <v>661913000</v>
       </c>
       <c r="BL5" t="n">
-        <v>4580000</v>
+        <v>204400000</v>
       </c>
       <c r="BM5" t="n">
-        <v>16032000</v>
+        <v>235659000</v>
       </c>
       <c r="BN5" t="n">
-        <v>88589000</v>
+        <v>16624000</v>
       </c>
       <c r="BO5" t="n">
-        <v>174009000</v>
+        <v>205230000</v>
       </c>
       <c r="BP5" t="n">
         <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1398970000</v>
+        <v>2403206000</v>
       </c>
       <c r="BR5" t="n">
-        <v>5521000</v>
+        <v>12082000</v>
       </c>
       <c r="BS5" t="n">
-        <v>847000</v>
+        <v>12728000</v>
       </c>
       <c r="BT5" t="n">
-        <v>154483000</v>
+        <v>216603000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4738000</v>
+        <v>15555000</v>
       </c>
       <c r="BV5" t="n">
-        <v>1504000</v>
+        <v>10145000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2515000</v>
+        <v>4364000</v>
       </c>
       <c r="BX5" t="n">
-        <v>719000</v>
+        <v>1046000</v>
       </c>
       <c r="BY5" t="n">
-        <v>87618000</v>
+        <v>54753000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>25334000</v>
+        <v>115874000</v>
       </c>
       <c r="CA5" t="n">
-        <v>116008000</v>
+        <v>187179000</v>
       </c>
       <c r="CB5" t="n">
-        <v>-4576000</v>
+        <v>-8530000</v>
       </c>
       <c r="CC5" t="n">
-        <v>120584000</v>
+        <v>195709000</v>
       </c>
       <c r="CD5" t="n">
-        <v>1004421000</v>
+        <v>1788432000</v>
       </c>
       <c r="CE5" t="n">
-        <v>39231000</v>
+        <v>269830000</v>
       </c>
       <c r="CF5" t="n">
-        <v>965190000</v>
-      </c>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
+        <v>1518602000</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>383018000</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1135584000</v>
+      </c>
+      <c r="CI5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C6" t="n">
+        <v>95991300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>123522000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99088000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1082208000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-308626000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>99088000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>122666000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1081352000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1081352000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1240978000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>159626000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1081352000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1014512000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3007100000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>346038000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>34254000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>15144000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>55388000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>65681000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>98665000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>98665000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>4527000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2661062000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>884921000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24857000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>24001000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>856000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>46579000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>15230000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>487536000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3901000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>102374000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>381261000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4248078000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1895643000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>30342000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>133645000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>37004000</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>5158000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5158000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>32462000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4321000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>27532000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>609000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>982264000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>248204000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>734060000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>638091000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-280118000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>918209000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>393171000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>274994000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>22028000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>228016000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2352436000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>5966000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>275378000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>20084000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>13361000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>5646000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1077000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>75939000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>149480000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>210643000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-7850000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>218493000</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1614946000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>259233000</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>1355713000</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>280194000</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1075519000</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-1000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2694,7 +2888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,580 +3135,641 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>329894000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1644000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1901000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-176525000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1518603000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1028493000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-2071000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>492181000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-193853000</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-2213000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-137268000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>257000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>257000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1644000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1901000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>179615000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>16276000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>416435000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>645432000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-228997000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-92440000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>26778000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-119218000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-33649000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-34249000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-127007000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>15269000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-142276000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>506419000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-178324000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>52849000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-12594000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>101338000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>196924000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>-37929000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-780000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-45690000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-76609000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>173029000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>93471000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>93471000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3042000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-343000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>350559000</v>
-      </c>
+        <v>-4439000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>459130000</v>
+        <v>293049000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1183000</v>
+        <v>-4305000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-170989000</v>
+        <v>-53523000</v>
       </c>
       <c r="F3" t="n">
-        <v>1028493000</v>
+        <v>1148850000</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>-296000</v>
       </c>
       <c r="H3" t="n">
-        <v>1148850000</v>
+        <v>1004952000</v>
       </c>
       <c r="I3" t="n">
-        <v>7901000</v>
+        <v>4474000</v>
       </c>
       <c r="J3" t="n">
-        <v>-128259000</v>
+        <v>139720000</v>
       </c>
       <c r="K3" t="n">
-        <v>-141638000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>12145000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-101751000</v>
-      </c>
+        <v>-29887000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-1183000</v>
+        <v>-4305000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1183000</v>
+        <v>-4305000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1183000</v>
+        <v>-4305000</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-616740000</v>
+        <v>-176965000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="T3" t="n">
-        <v>28716000</v>
+        <v>3732000</v>
       </c>
       <c r="U3" t="n">
-        <v>-483265000</v>
+        <v>-133994000</v>
       </c>
       <c r="V3" t="n">
-        <v>168136000</v>
+        <v>10094000</v>
       </c>
       <c r="W3" t="n">
-        <v>-651401000</v>
+        <v>-144088000</v>
       </c>
       <c r="X3" t="n">
-        <v>8219000</v>
+        <v>6430000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12150000</v>
+        <v>15475000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3931000</v>
+        <v>-9045000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-31526000</v>
+        <v>-24471000</v>
       </c>
       <c r="AB3" t="n">
-        <v>39000</v>
+        <v>286000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-31565000</v>
+        <v>-24757000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-138883000</v>
+        <v>-28660000</v>
       </c>
       <c r="AE3" t="n">
-        <v>541000</v>
+        <v>106000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-139424000</v>
+        <v>-28766000</v>
       </c>
       <c r="AG3" t="n">
-        <v>630119000</v>
+        <v>346572000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-161851000</v>
+        <v>-36545000</v>
       </c>
       <c r="AI3" t="n">
-        <v>26237000</v>
+        <v>3631000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-6000000</v>
+        <v>-2062000</v>
       </c>
       <c r="AK3" t="n">
-        <v>279121000</v>
+        <v>10301000</v>
       </c>
       <c r="AL3" t="n">
-        <v>310690000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>33415000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-132964000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>5066000</v>
+        <v>34741000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2662000</v>
+        <v>-840000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-19550000</v>
+        <v>-72784000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-11373000</v>
+        <v>-16804000</v>
       </c>
       <c r="AR3" t="n">
-        <v>135580000</v>
+        <v>87472000</v>
       </c>
       <c r="AS3" t="n">
-        <v>91635000</v>
+        <v>60689000</v>
       </c>
       <c r="AT3" t="n">
-        <v>91635000</v>
+        <v>60689000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3645000</v>
+        <v>-7511000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-399000</v>
+        <v>-6324000</v>
       </c>
       <c r="AW3" t="n">
-        <v>273524000</v>
+        <v>253725000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>293049000</v>
+        <v>459130000</v>
       </c>
       <c r="C4" t="n">
-        <v>-4305000</v>
+        <v>-1183000</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-53523000</v>
+        <v>-170989000</v>
       </c>
       <c r="F4" t="n">
+        <v>1028493000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
         <v>1148850000</v>
       </c>
-      <c r="G4" t="n">
-        <v>-296000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1004952000</v>
-      </c>
       <c r="I4" t="n">
-        <v>4474000</v>
+        <v>7901000</v>
       </c>
       <c r="J4" t="n">
-        <v>139720000</v>
+        <v>-128259000</v>
       </c>
       <c r="K4" t="n">
-        <v>-29887000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>-141638000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12145000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-101751000</v>
+      </c>
       <c r="N4" t="n">
-        <v>-4305000</v>
+        <v>-1183000</v>
       </c>
       <c r="O4" t="n">
-        <v>-4305000</v>
+        <v>-1183000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4305000</v>
+        <v>-1183000</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-176965000</v>
+        <v>-616740000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="n">
-        <v>3732000</v>
+        <v>28716000</v>
       </c>
       <c r="U4" t="n">
-        <v>-133994000</v>
+        <v>-483265000</v>
       </c>
       <c r="V4" t="n">
-        <v>10094000</v>
+        <v>168136000</v>
       </c>
       <c r="W4" t="n">
-        <v>-144088000</v>
+        <v>-651401000</v>
       </c>
       <c r="X4" t="n">
-        <v>6430000</v>
+        <v>8219000</v>
       </c>
       <c r="Y4" t="n">
-        <v>15475000</v>
+        <v>12150000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-9045000</v>
+        <v>-3931000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-24471000</v>
+        <v>-31526000</v>
       </c>
       <c r="AB4" t="n">
-        <v>286000</v>
+        <v>39000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-24757000</v>
+        <v>-31565000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-28660000</v>
+        <v>-138883000</v>
       </c>
       <c r="AE4" t="n">
-        <v>106000</v>
+        <v>541000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-28766000</v>
+        <v>-139424000</v>
       </c>
       <c r="AG4" t="n">
-        <v>346572000</v>
+        <v>630119000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-36545000</v>
+        <v>-161851000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3631000</v>
+        <v>26237000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2062000</v>
+        <v>-6000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>10301000</v>
+        <v>279121000</v>
       </c>
       <c r="AL4" t="n">
-        <v>33415000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-132964000</v>
-      </c>
+        <v>310690000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>34741000</v>
+        <v>5066000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-840000</v>
+        <v>-2662000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-72784000</v>
+        <v>-19550000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-16804000</v>
+        <v>-11373000</v>
       </c>
       <c r="AR4" t="n">
-        <v>87472000</v>
+        <v>135580000</v>
       </c>
       <c r="AS4" t="n">
-        <v>60689000</v>
+        <v>91635000</v>
       </c>
       <c r="AT4" t="n">
-        <v>60689000</v>
+        <v>91635000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-7511000</v>
+        <v>3645000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-6324000</v>
+        <v>-399000</v>
       </c>
       <c r="AW4" t="n">
-        <v>253725000</v>
+        <v>273524000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>467703000</v>
+        <v>329894000</v>
       </c>
       <c r="C5" t="n">
-        <v>-200357000</v>
+        <v>-1644000</v>
       </c>
       <c r="D5" t="n">
-        <v>323000</v>
+        <v>1901000</v>
       </c>
       <c r="E5" t="n">
-        <v>-35038000</v>
+        <v>-176525000</v>
       </c>
       <c r="F5" t="n">
-        <v>965190000</v>
+        <v>1518603000</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>741182000</v>
+        <v>1028493000</v>
       </c>
       <c r="I5" t="n">
-        <v>6572000</v>
+        <v>-2071000</v>
       </c>
       <c r="J5" t="n">
-        <v>217436000</v>
+        <v>492181000</v>
       </c>
       <c r="K5" t="n">
-        <v>-222682000</v>
+        <v>-193853000</v>
       </c>
       <c r="L5" t="n">
-        <v>-4439000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-2213000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-137268000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-200034000</v>
+        <v>257000</v>
       </c>
       <c r="O5" t="n">
-        <v>-200034000</v>
+        <v>257000</v>
       </c>
       <c r="P5" t="n">
-        <v>-200357000</v>
+        <v>-1644000</v>
       </c>
       <c r="Q5" t="n">
-        <v>323000</v>
+        <v>1901000</v>
       </c>
       <c r="R5" t="n">
-        <v>-62623000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1000</v>
-      </c>
+        <v>179615000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1811000</v>
+        <v>16276000</v>
       </c>
       <c r="U5" t="n">
-        <v>43000</v>
+        <v>416435000</v>
       </c>
       <c r="V5" t="n">
-        <v>44000</v>
+        <v>645432000</v>
       </c>
       <c r="W5" t="n">
+        <v>-228997000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-92440000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>26778000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-119218000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-33649000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-34249000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-127007000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>15269000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-142276000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>506419000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-178324000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>52849000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-12594000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>101338000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>196924000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>-37929000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-780000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-45690000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-76609000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>173029000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>93471000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>93471000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3042000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-343000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>350559000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>85842000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-2383000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-278905000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1355713000</v>
+      </c>
+      <c r="G6" t="n">
         <v>-1000</v>
       </c>
-      <c r="X5" t="n">
-        <v>-30139000</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>-30139000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-22180000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>526000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-22706000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-12159000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>173000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-12332000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>502741000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-31420000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>654000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-2955000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>336877000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>529822000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-30000000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-67861000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>332000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-89345000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6273000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>47835000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55501000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>55501000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-3229000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-62000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>93269000</v>
+      <c r="H6" t="n">
+        <v>1518603000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-10117000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-152772000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-226173000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20370000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-159346000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-2310000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2310000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2383000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>73000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-291346000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>2950000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-21722000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>268638000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-290360000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3983000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3983000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-42702000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-42705000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-233855000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-236200000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>364747000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-201714000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>31148000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-8739000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-24767000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>184820000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>-55930000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1557000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-146841000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10505000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>154717000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>101601000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>101601000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-1002000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1439000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>304436000</v>
       </c>
     </row>
   </sheetData>
@@ -4069,187 +4324,187 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -4269,10 +4524,8 @@
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20354</t>
-        </is>
+      <c r="C2" t="n">
+        <v>20354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4353,7 +4606,7 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4370,70 +4623,70 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>60.55</v>
+        <v>54.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>61.75</v>
+        <v>54.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>61.75</v>
+        <v>51.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>61.75</v>
+        <v>54.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>60.55</v>
+        <v>54.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>61.75</v>
+        <v>54.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>61.75</v>
+        <v>51.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>61.75</v>
+        <v>54.15</v>
       </c>
       <c r="AI2" t="n">
         <v>1.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="AK2" t="n">
         <v>1779926400</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.5552</v>
+        <v>0.5407</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.116</v>
+        <v>1.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.234114</v>
+        <v>16.775244</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AP2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AQ2" t="n">
         <v>18</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>57.6</v>
+        <v>44.44</v>
       </c>
       <c r="AU2" t="n">
-        <v>60.25</v>
+        <v>56.65</v>
       </c>
       <c r="AV2" t="n">
-        <v>5869867995</v>
+        <v>5212327590</v>
       </c>
       <c r="AW2" t="n">
         <v>49.14</v>
@@ -4448,16 +4701,16 @@
         <v>49.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>56.942</v>
+        <v>56.626</v>
       </c>
       <c r="BB2" t="n">
-        <v>60.391304</v>
+        <v>60.391216</v>
       </c>
       <c r="BC2" t="n">
         <v>1.44</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.023782</v>
+        <v>0.026592799</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4468,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>4690653696</v>
+        <v>4081108992</v>
       </c>
       <c r="BH2" t="n">
         <v>0.09231</v>
@@ -4480,13 +4733,13 @@
         <v>0.38827</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.40202</v>
+        <v>0.39499</v>
       </c>
       <c r="BL2" t="n">
         <v>11.966</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.055992</v>
+        <v>4.303861</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4504,19 +4757,19 @@
         <v>294864000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.468</v>
+        <v>1.278</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.968999999999999</v>
+        <v>7.804</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.07399106</v>
+        <v>-0.19058293</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27449715</v>
+        <v>0.22635591</v>
       </c>
       <c r="BX2" t="n">
         <v>1.44</v>
@@ -4530,7 +4783,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4634,97 +4887,95 @@
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>1780039621</v>
+      <c r="DE2" t="n">
+        <v>1780909509</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>finmb_5598951</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>finmb_5598951</t>
+          <t>Europe/Rome</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DJ2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>it_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>CTS Eventim</t>
         </is>
       </c>
-      <c r="DO2" t="b">
+      <c r="DN2" t="b">
         <v>0</v>
       </c>
+      <c r="DO2" t="n">
+        <v>1772006400000</v>
+      </c>
       <c r="DP2" t="n">
-        <v>1772006400000</v>
+        <v>-4.8938165</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.049999237</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>61.75 - 61.75</t>
-        </is>
+        <v>51.5</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-2.6500015</v>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
+          <t>51.5 - 54.15</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DT2" t="n">
+      <c r="DU2" t="n">
         <v>18</v>
       </c>
-      <c r="DU2" t="n">
-        <v>11.360001</v>
-      </c>
       <c r="DV2" t="n">
-        <v>0.23117624</v>
-      </c>
-      <c r="DW2" t="inlineStr">
+        <v>2.3600006</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.048026063</v>
+      </c>
+      <c r="DX2" t="inlineStr">
         <is>
           <t>49.14 - 74.1</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>-13.599998</v>
-      </c>
       <c r="DY2" t="n">
-        <v>-0.18353574</v>
+        <v>-22.599998</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-7.399106</v>
+        <v>-0.30499324</v>
       </c>
       <c r="EA2" t="n">
-        <v>1787239800</v>
+        <v>-19.058292</v>
       </c>
       <c r="EB2" t="n">
         <v>1787239800</v>
@@ -4732,38 +4983,40 @@
       <c r="EC2" t="n">
         <v>1787239800</v>
       </c>
-      <c r="ED2" t="b">
+      <c r="ED2" t="n">
+        <v>1787239800</v>
+      </c>
+      <c r="EE2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>2.99</v>
-      </c>
       <c r="EF2" t="n">
-        <v>3.5579987</v>
+        <v>3.07</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.062484607</v>
+        <v>-5.1259995</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.108695984</v>
+        <v>-0.09052378</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0017998616</v>
+        <v>-8.891216</v>
       </c>
       <c r="EJ2" t="n">
+        <v>-0.14722697</v>
+      </c>
+      <c r="EK2" t="n">
         <v>20</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="EL2" t="n">
         <v>15</v>
       </c>
-      <c r="EL2" t="b">
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>POSTPOST</t>
+        </is>
+      </c>
+      <c r="EN2" t="b">
         <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.08257512</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>60.5</v>
       </c>
       <c r="EO2" t="inlineStr"/>
     </row>
